--- a/山海企划-BOM与预算.xlsx
+++ b/山海企划-BOM与预算.xlsx
@@ -843,17 +843,17 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>A 服务器与计算</t>
+          <t>A 云资源与计算</t>
         </is>
       </c>
       <c r="C2" s="7" t="inlineStr">
         <is>
-          <t>F1 交易服务器</t>
+          <t>云服务器·前端聚合（F1+F2）</t>
         </is>
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>4C/8G/256G SSD 迷你主机（N100 级及以上），Debian 12，跑 shs-trade</t>
+          <t>华为云 ECS 16C32G，系统盘+数据盘 500G，EIP 带宽峰值 500M（按流量计费）；TLS 网关 SNI 分流 api/static；shs-catalog + shs-trade 双进程</t>
         </is>
       </c>
       <c r="E2" s="8" t="n">
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="G2" s="9" t="n">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="H2" s="9" t="n">
-        <v>1500</v>
+        <v>3200</v>
       </c>
       <c r="I2" s="8">
         <f>E2*G2</f>
@@ -888,12 +888,12 @@
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>建议向学校/社团征借</t>
+          <t>包月 1–2 个月，活动后释放/降配；4C8G 即满足论证容量，16C32G 为余量/复用选择</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>A 服务器与计算</t>
+          <t>A 云资源与计算</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>BE 账本服务器</t>
+          <t>云服务器·BE（账本）</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>同 A1，跑 shs-core，配 U 盘备份位</t>
+          <t>华为云 ECS 2C4G，数据盘 40G，公网 IP；shs-core</t>
         </is>
       </c>
       <c r="E3" s="8" t="n">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="G3" s="9" t="n">
-        <v>1100</v>
+        <v>150</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="I3" s="8">
         <f>E3*G3</f>
@@ -950,12 +950,12 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>建议征借</t>
+          <t>与聚合机分离保留故障域</t>
         </is>
       </c>
     </row>
@@ -967,17 +967,17 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>A 服务器与计算</t>
+          <t>A 云资源与计算</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>F2 目录服务器</t>
+          <t>CDN 流量包</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>4C/8G/500G SSD（商品图片存储），跑 shs-catalog</t>
+          <t>≥100GB；图片/静态边缘分流≈90% 读流量；/api/* 一律不缓存</t>
         </is>
       </c>
       <c r="E4" s="8" t="n">
@@ -985,14 +985,14 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>台</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G4" s="9" t="n">
-        <v>1200</v>
+        <v>20</v>
       </c>
       <c r="H4" s="9" t="n">
-        <v>1700</v>
+        <v>60</v>
       </c>
       <c r="I4" s="8">
         <f>E4*G4</f>
@@ -1012,14 +1012,10 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N4" s="7" t="inlineStr">
-        <is>
-          <t>建议征借</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -1029,17 +1025,17 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>A 服务器与计算</t>
+          <t>A 云资源与计算</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>运维笔记本</t>
+          <t>域名 + SSL 证书</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>任意可用笔记本：SSH/监控大屏/备份/可选 dnsmasq</t>
+          <t>备案域名一年 + 云免费证书 ×3（edge/be/static）</t>
         </is>
       </c>
       <c r="E5" s="8" t="n">
@@ -1047,14 +1043,14 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>台</t>
+          <t>项</t>
         </is>
       </c>
       <c r="G5" s="9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5" s="8">
         <f>E5*G5</f>
@@ -1074,12 +1070,12 @@
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>仅征借；全新档不适用</t>
+          <t>★ 备案周期 1–3 周，W1 立即启动</t>
         </is>
       </c>
     </row>
@@ -1091,21 +1087,21 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>A 服务器与计算</t>
+          <t>A 云资源与计算</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>系统 U 盘</t>
+          <t>对象存储（可选）</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>32G USB3 ×2（安装介质+应急启动盘）</t>
+          <t>50GB 备份桶（数据三备份介质之一）</t>
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
@@ -1113,10 +1109,10 @@
         </is>
       </c>
       <c r="G6" s="9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H6" s="9" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I6" s="8">
         <f>E6*G6</f>
@@ -1139,7 +1135,11 @@
           <t>否</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr"/>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>可用云盘快照替代</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1149,32 +1149,32 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>A 服务器与计算</t>
+          <t>A 云资源与计算</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>备份 U 盘</t>
+          <t>运维笔记本</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>64G USB3 ×2（活动数据三备份双介质，活动结束当场带离）</t>
+          <t>现场管理/监控大屏/离线备份，SSH 密钥</t>
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>台</t>
         </is>
       </c>
       <c r="G7" s="9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H7" s="9" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="I7" s="8">
         <f>E7*G7</f>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>★ 安全库存必须</t>
+          <t>仅征借</t>
         </is>
       </c>
     </row>
@@ -1211,32 +1211,32 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>A 服务器与计算</t>
+          <t>A 云资源与计算</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>入口大屏动态码终端</t>
+          <t>备份 U 盘</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>平板/笔记本/一体机，横屏 ≥10 英寸（每 2s 刷新入场码）</t>
+          <t>64G USB3 ×2（账本离线双介质，活动结束当场带离）</t>
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>台</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G8" s="9" t="n">
-        <v>800</v>
+        <v>35</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1200</v>
+        <v>60</v>
       </c>
       <c r="I8" s="8">
         <f>E8*G8</f>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>配支架</t>
+          <t>★ 安全库存必须</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>A 服务器与计算</t>
+          <t>A 云资源与计算</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>大屏支架/桌架</t>
+          <t>入口大屏动态码终端</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>落地或桌面支架，顾客扫码高度约 1.2m</t>
+          <t>平板/笔记本/一体机，横屏 ≥10 英寸（每 2s 刷新入场码）</t>
         </is>
       </c>
       <c r="E9" s="8" t="n">
@@ -1291,14 +1291,14 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>台</t>
         </is>
       </c>
       <c r="G9" s="9" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>150</v>
+        <v>1200</v>
       </c>
       <c r="I9" s="8">
         <f>E9*G9</f>
@@ -1318,77 +1318,77 @@
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>配支架</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>A 云资源与计算</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>大屏支架/桌架</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>落地或桌面支架，顾客扫码高度约 1.2m</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="I10" s="8">
+        <f>E10*G10</f>
+        <v/>
+      </c>
+      <c r="J10" s="8">
+        <f>E10*H10</f>
+        <v/>
+      </c>
+      <c r="K10" s="8">
+        <f>IF($M10="是",0,I10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="8">
+        <f>IF($M10="是",0,J10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
-      <c r="N9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>B 网络设备</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
-        <is>
-          <t>QCI6 CPE（主）</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>5G/4G CPE，带千兆 LAN + Wi-Fi，现场出口</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>台</t>
-        </is>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>400</v>
-      </c>
-      <c r="H10" s="13" t="n">
-        <v>700</v>
-      </c>
-      <c r="I10" s="12">
-        <f>E10*G10</f>
-        <v/>
-      </c>
-      <c r="J10" s="12">
-        <f>E10*H10</f>
-        <v/>
-      </c>
-      <c r="K10" s="12">
-        <f>IF($M10="是",0,I10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="12">
-        <f>IF($M10="是",0,J10)</f>
-        <v/>
-      </c>
-      <c r="M10" s="10" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>出口仅 NTP/管理</t>
-        </is>
-      </c>
+      <c r="N10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="B11" s="10" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>QCI6 CPE（备）</t>
+          <t>QCI6 CPE（主）</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>同上，冷备换插即用 ≤5min</t>
+          <t>5G/4G CPE，带千兆 LAN + Wi-Fi，现场统一出口</t>
         </is>
       </c>
       <c r="E11" s="12" t="n">
@@ -1443,14 +1443,14 @@
       </c>
       <c r="N11" s="11" t="inlineStr">
         <is>
-          <t>异网 SIM</t>
+          <t>出口仅 API 流量（CDN 已卸载图片）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="B12" s="10" t="inlineStr">
@@ -1460,27 +1460,27 @@
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>数据 SIM 卡</t>
+          <t>QCI6 CPE（备）</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>流量包 ≥20G/卡，分属两家运营商</t>
+          <t>同上，冷备换插即用 ≤5min</t>
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>张</t>
+          <t>台</t>
         </is>
       </c>
       <c r="G12" s="13" t="n">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>60</v>
+        <v>700</v>
       </c>
       <c r="I12" s="12">
         <f>E12*G12</f>
@@ -1505,14 +1505,14 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>★ 异网冗余</t>
+          <t>异网 SIM</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B13" s="10" t="inlineStr">
@@ -1522,27 +1522,27 @@
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>核心路由器</t>
+          <t>数据 SIM 卡</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>千兆，可刷 OpenWrt（防火墙/静态路由/DNS）</t>
+          <t>流量包 ≥20G/卡，分属两家运营商</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>台</t>
+          <t>张</t>
         </is>
       </c>
       <c r="G13" s="13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I13" s="12">
         <f>E13*G13</f>
@@ -1562,19 +1562,19 @@
       </c>
       <c r="M13" s="10" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="N13" s="11" t="inlineStr">
         <is>
-          <t>或 CPE 路由模式直挂</t>
+          <t>已办理√（存量）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>B5</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="B14" s="10" t="inlineStr">
@@ -1584,12 +1584,12 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>交换机 SW1</t>
+          <t>核心路由器</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>8 口千兆非网管（服务器区）</t>
+          <t>千兆，可刷 OpenWrt（防火墙/静态路由/DNS）</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="G14" s="13" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="I14" s="12">
         <f>E14*G14</f>
@@ -1624,15 +1624,19 @@
       </c>
       <c r="M14" s="10" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N14" s="11" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N14" s="11" t="inlineStr">
+        <is>
+          <t>或 CPE 路由模式直挂</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>B6</t>
+          <t>B5</t>
         </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1642,12 +1646,12 @@
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>PoE 交换机 SW2</t>
+          <t>交换机 SW1</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>8 口千兆 PoE（AP 供电）</t>
+          <t>8 口千兆非网管（运维本/大屏/打印机）</t>
         </is>
       </c>
       <c r="E15" s="12" t="n">
@@ -1659,10 +1663,10 @@
         </is>
       </c>
       <c r="G15" s="13" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="I15" s="12">
         <f>E15*G15</f>
@@ -1685,16 +1689,12 @@
           <t>否</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>或 PoE 注入器 ×3 可省约 200</t>
-        </is>
-      </c>
+      <c r="N15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t>B7</t>
+          <t>B6</t>
         </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1704,16 +1704,16 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Wi-Fi 6 AP</t>
+          <t>PoE 交换机 SW2</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>双频 AX3000 级，多 SSID（入口/队伍、提货/纪念、浏览/机动）</t>
+          <t>8 口千兆 PoE（AP 供电）</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
@@ -1721,10 +1721,10 @@
         </is>
       </c>
       <c r="G16" s="13" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="H16" s="13" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="I16" s="12">
         <f>E16*G16</f>
@@ -1749,14 +1749,14 @@
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>单 AP 建议 ≤80 终端</t>
+          <t>或 PoE 注入器 ×3 可省约 200</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t>B8</t>
+          <t>B7</t>
         </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1766,27 +1766,27 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>网线与配件</t>
+          <t>Wi-Fi 6 AP</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>Cat6 成品线 1m/3m/10m 合计 12 根 + 水晶头工具包（含备线 4 根）</t>
+          <t>双频 AX3000 级，多 SSID（入口/队伍、提货/纪念、浏览/机动）</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F17" s="10" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>台</t>
         </is>
       </c>
       <c r="G17" s="13" t="n">
-        <v>120</v>
+        <v>250</v>
       </c>
       <c r="H17" s="13" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="I17" s="12">
         <f>E17*G17</f>
@@ -1811,14 +1811,14 @@
       </c>
       <c r="N17" s="11" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>单 AP 建议 ≤80 终端</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>B9</t>
+          <t>B8</t>
         </is>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>测线仪/寻线器</t>
+          <t>网线与配件</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>简易网络测线仪</t>
+          <t>Cat6 成品线 1m/3m/10m 合计 12 根 + 水晶头工具包（含备线 4 根）</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
@@ -1841,14 +1841,14 @@
       </c>
       <c r="F18" s="10" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>套</t>
         </is>
       </c>
       <c r="G18" s="13" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="H18" s="13" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="I18" s="12">
         <f>E18*G18</f>
@@ -1871,74 +1871,74 @@
           <t>否</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>C1</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>C 员工终端与外设</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
-        <is>
-          <t>员工手机</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>安卓 ≥8.0、支持 BLE（个人机征用优先），分配见部署手册</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>台</t>
-        </is>
-      </c>
-      <c r="G19" s="17" t="n">
-        <v>600</v>
-      </c>
-      <c r="H19" s="17" t="n">
-        <v>1200</v>
-      </c>
-      <c r="I19" s="16">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>B 网络设备</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>测线仪/寻线器</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>简易网络测线仪</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="I19" s="12">
         <f>E19*G19</f>
         <v/>
       </c>
-      <c r="J19" s="16">
+      <c r="J19" s="12">
         <f>E19*H19</f>
         <v/>
       </c>
-      <c r="K19" s="16">
+      <c r="K19" s="12">
         <f>IF($M19="是",0,I19)</f>
         <v/>
       </c>
-      <c r="L19" s="16">
+      <c r="L19" s="12">
         <f>IF($M19="是",0,J19)</f>
         <v/>
       </c>
-      <c r="M19" s="14" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="N19" s="15" t="inlineStr">
-        <is>
-          <t>入口2/队列3/配货2/提货2/纪念1</t>
-        </is>
-      </c>
+      <c r="M19" s="10" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -1948,16 +1948,16 @@
       </c>
       <c r="C20" s="15" t="inlineStr">
         <is>
-          <t>管理平板</t>
+          <t>员工手机</t>
         </is>
       </c>
       <c r="D20" s="15" t="inlineStr">
         <is>
-          <t>安卓平板 ≥10 英寸（ADMIN 大屏+走动指挥）</t>
+          <t>安卓 ≥8.0、支持 BLE（个人机征用优先），分配见部署手册</t>
         </is>
       </c>
       <c r="E20" s="16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="G20" s="17" t="n">
-        <v>900</v>
+        <v>600</v>
       </c>
       <c r="H20" s="17" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="I20" s="16">
         <f>E20*G20</f>
@@ -1991,12 +1991,16 @@
           <t>是</t>
         </is>
       </c>
-      <c r="N20" s="15" t="inlineStr"/>
+      <c r="N20" s="15" t="inlineStr">
+        <is>
+          <t>入口2/队列3/配货2/提货2/纪念1</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -2006,16 +2010,16 @@
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>热敏小票打印机</t>
+          <t>管理平板</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>58mm 蓝牙（佳博/芯烨类），ESC/POS；配货区×2+提货区热备×1</t>
+          <t>安卓平板 ≥10 英寸（ADMIN 大屏+走动指挥）</t>
         </is>
       </c>
       <c r="E21" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
@@ -2023,10 +2027,10 @@
         </is>
       </c>
       <c r="G21" s="17" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="H21" s="17" t="n">
-        <v>320</v>
+        <v>1500</v>
       </c>
       <c r="I21" s="16">
         <f>E21*G21</f>
@@ -2046,19 +2050,15 @@
       </c>
       <c r="M21" s="14" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N21" s="15" t="inlineStr">
-        <is>
-          <t>★ 最高频故障点</t>
-        </is>
-      </c>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="N21" s="15" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
@@ -2068,27 +2068,27 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>热敏纸卷</t>
+          <t>热敏小票打印机</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>57×30mm（约 250 张/卷）；按峰值 3000 单×2 联冗余</t>
+          <t>58mm 蓝牙（佳博/芯烨类），ESC/POS；配货区×2+提货区热备×1</t>
         </is>
       </c>
       <c r="E22" s="16" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>卷</t>
+          <t>台</t>
         </is>
       </c>
       <c r="G22" s="17" t="n">
-        <v>1.5</v>
+        <v>180</v>
       </c>
       <c r="H22" s="17" t="n">
-        <v>2.5</v>
+        <v>320</v>
       </c>
       <c r="I22" s="16">
         <f>E22*G22</f>
@@ -2113,14 +2113,14 @@
       </c>
       <c r="N22" s="15" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★ 最高频故障点</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
@@ -2130,27 +2130,27 @@
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>打印机电源/线材</t>
+          <t>热敏纸卷</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>原配 DC 线 + USB 兜底线</t>
+          <t>57×30mm（约 250 张/卷）；按峰值 3000 单×2 联冗余</t>
         </is>
       </c>
       <c r="E23" s="16" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>卷</t>
         </is>
       </c>
       <c r="G23" s="17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="H23" s="17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I23" s="16">
         <f>E23*G23</f>
@@ -2175,72 +2175,76 @@
       </c>
       <c r="N23" s="15" t="inlineStr">
         <is>
+          <t>★</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>C 员工终端与外设</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>打印机电源/线材</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>原配 DC 线 + USB 兜底线</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="16">
+        <f>E24*G24</f>
+        <v/>
+      </c>
+      <c r="J24" s="16">
+        <f>E24*H24</f>
+        <v/>
+      </c>
+      <c r="K24" s="16">
+        <f>IF($M24="是",0,I24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="16">
+        <f>IF($M24="是",0,J24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="N24" s="15" t="inlineStr">
+        <is>
           <t>随机附带</t>
         </is>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>D 电源与续航</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>UPS</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>500–650VA ×3（服务器各一）或 1 台 1kVA + PDU；断电撑 ≥30min</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>台</t>
-        </is>
-      </c>
-      <c r="G24" s="21" t="n">
-        <v>200</v>
-      </c>
-      <c r="H24" s="21" t="n">
-        <v>350</v>
-      </c>
-      <c r="I24" s="20">
-        <f>E24*G24</f>
-        <v/>
-      </c>
-      <c r="J24" s="20">
-        <f>E24*H24</f>
-        <v/>
-      </c>
-      <c r="K24" s="20">
-        <f>IF($M24="是",0,I24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="20">
-        <f>IF($M24="是",0,J24)</f>
-        <v/>
-      </c>
-      <c r="M24" s="18" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N24" s="19" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
@@ -2250,27 +2254,27 @@
       </c>
       <c r="C25" s="19" t="inlineStr">
         <is>
-          <t>大功率充电宝</t>
+          <t>小型 UPS（可选）</t>
         </is>
       </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
-          <t>20,000mAh PD 30W+，员工终端全岗位覆盖</t>
+          <t>现场网络设备（AP/交换机/CPE）断电续航 ≥30min</t>
         </is>
       </c>
       <c r="E25" s="20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F25" s="18" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>台</t>
         </is>
       </c>
       <c r="G25" s="21" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="H25" s="21" t="n">
-        <v>180</v>
+        <v>350</v>
       </c>
       <c r="I25" s="20">
         <f>E25*G25</f>
@@ -2295,14 +2299,14 @@
       </c>
       <c r="N25" s="19" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>服务器在云端，无需大 UPS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
@@ -2312,16 +2316,16 @@
       </c>
       <c r="C26" s="19" t="inlineStr">
         <is>
-          <t>多口充电器</t>
+          <t>大功率充电宝</t>
         </is>
       </c>
       <c r="D26" s="19" t="inlineStr">
         <is>
-          <t>65W GaN 3 口，指挥台集中补电</t>
+          <t>20,000mAh PD 30W+，员工终端全岗位覆盖</t>
         </is>
       </c>
       <c r="E26" s="20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F26" s="18" t="inlineStr">
         <is>
@@ -2329,10 +2333,10 @@
         </is>
       </c>
       <c r="G26" s="21" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H26" s="21" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="I26" s="20">
         <f>E26*G26</f>
@@ -2355,12 +2359,16 @@
           <t>否</t>
         </is>
       </c>
-      <c r="N26" s="19" t="inlineStr"/>
+      <c r="N26" s="19" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
@@ -2370,16 +2378,16 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>插线板</t>
+          <t>多口充电器</t>
         </is>
       </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
-          <t>6 位 ×1.8m 安全长款，各工位</t>
+          <t>65W GaN 3 口，指挥台集中补电</t>
         </is>
       </c>
       <c r="E27" s="20" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F27" s="18" t="inlineStr">
         <is>
@@ -2387,10 +2395,10 @@
         </is>
       </c>
       <c r="G27" s="21" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="H27" s="21" t="n">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="I27" s="20">
         <f>E27*G27</f>
@@ -2418,7 +2426,7 @@
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
@@ -2428,27 +2436,27 @@
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>手机备用数据线</t>
+          <t>插线板</t>
         </is>
       </c>
       <c r="D28" s="19" t="inlineStr">
         <is>
-          <t>USB-C/Lightning 混装（易耗必损件）</t>
+          <t>6 位 ×1.8m 安全长款，各工位</t>
         </is>
       </c>
       <c r="E28" s="20" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>根</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G28" s="21" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="H28" s="21" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="I28" s="20">
         <f>E28*G28</f>
@@ -2471,74 +2479,74 @@
           <t>否</t>
         </is>
       </c>
-      <c r="N28" s="19" t="inlineStr">
+      <c r="N28" s="19" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>D 电源与续航</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr">
+        <is>
+          <t>手机备用数据线</t>
+        </is>
+      </c>
+      <c r="D29" s="19" t="inlineStr">
+        <is>
+          <t>USB-C/Lightning 混装（易耗必损件）</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="F29" s="18" t="inlineStr">
+        <is>
+          <t>根</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="H29" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="I29" s="20">
+        <f>E29*G29</f>
+        <v/>
+      </c>
+      <c r="J29" s="20">
+        <f>E29*H29</f>
+        <v/>
+      </c>
+      <c r="K29" s="20">
+        <f>IF($M29="是",0,I29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="20">
+        <f>IF($M29="是",0,J29)</f>
+        <v/>
+      </c>
+      <c r="M29" s="18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="N29" s="19" t="inlineStr">
         <is>
           <t>★</t>
         </is>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="22" t="inlineStr">
-        <is>
-          <t>E1</t>
-        </is>
-      </c>
-      <c r="B29" s="22" t="inlineStr">
-        <is>
-          <t>E 通信与现场物料</t>
-        </is>
-      </c>
-      <c r="C29" s="23" t="inlineStr">
-        <is>
-          <t>对讲机</t>
-        </is>
-      </c>
-      <c r="D29" s="23" t="inlineStr">
-        <is>
-          <t>民用 409MHz 免执照（网络降级时的沟通保障）</t>
-        </is>
-      </c>
-      <c r="E29" s="24" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" s="22" t="inlineStr">
-        <is>
-          <t>台</t>
-        </is>
-      </c>
-      <c r="G29" s="25" t="n">
-        <v>60</v>
-      </c>
-      <c r="H29" s="25" t="n">
-        <v>120</v>
-      </c>
-      <c r="I29" s="24">
-        <f>E29*G29</f>
-        <v/>
-      </c>
-      <c r="J29" s="24">
-        <f>E29*H29</f>
-        <v/>
-      </c>
-      <c r="K29" s="24">
-        <f>IF($M29="是",0,I29)</f>
-        <v/>
-      </c>
-      <c r="L29" s="24">
-        <f>IF($M29="是",0,J29)</f>
-        <v/>
-      </c>
-      <c r="M29" s="22" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="N29" s="23" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>E1</t>
         </is>
       </c>
       <c r="B30" s="22" t="inlineStr">
@@ -2548,27 +2556,27 @@
       </c>
       <c r="C30" s="23" t="inlineStr">
         <is>
-          <t>指引物料</t>
+          <t>对讲机</t>
         </is>
       </c>
       <c r="D30" s="23" t="inlineStr">
         <is>
-          <t>入口二维码立牌、流程指引海报 ×6、隐私公示牌（含数据30天销毁声明）</t>
+          <t>民用 409MHz 免执照（网络降级时的沟通保障）</t>
         </is>
       </c>
       <c r="E30" s="24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F30" s="22" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>台</t>
         </is>
       </c>
       <c r="G30" s="25" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="H30" s="25" t="n">
-        <v>400</v>
+        <v>120</v>
       </c>
       <c r="I30" s="24">
         <f>E30*G30</f>
@@ -2596,7 +2604,7 @@
     <row r="31">
       <c r="A31" s="22" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="B31" s="22" t="inlineStr">
@@ -2606,27 +2614,27 @@
       </c>
       <c r="C31" s="23" t="inlineStr">
         <is>
-          <t>桌牌/工牌</t>
+          <t>指引物料</t>
         </is>
       </c>
       <c r="D31" s="23" t="inlineStr">
         <is>
-          <t>分区胸牌：ENTRY蓝/QUEUE绿/PICKUP橙/SOUVENIR紫/ADMIN红</t>
+          <t>入口二维码立牌、流程指引海报 ×6、隐私公示牌（含数据30天销毁声明）</t>
         </is>
       </c>
       <c r="E31" s="24" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F31" s="22" t="inlineStr">
         <is>
-          <t>个</t>
+          <t>套</t>
         </is>
       </c>
       <c r="G31" s="25" t="n">
-        <v>5</v>
+        <v>200</v>
       </c>
       <c r="H31" s="25" t="n">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="I31" s="24">
         <f>E31*G31</f>
@@ -2654,7 +2662,7 @@
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="B32" s="22" t="inlineStr">
@@ -2664,27 +2672,27 @@
       </c>
       <c r="C32" s="23" t="inlineStr">
         <is>
-          <t>登记本+文具</t>
+          <t>桌牌/工牌</t>
         </is>
       </c>
       <c r="D32" s="23" t="inlineStr">
         <is>
-          <t>半离线应急登记本 ×3、笔、垫板（RB-04 兜底）</t>
+          <t>分区胸牌：ENTRY蓝/QUEUE绿/PICKUP橙/SOUVENIR紫/ADMIN红</t>
         </is>
       </c>
       <c r="E32" s="24" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="F32" s="22" t="inlineStr">
         <is>
-          <t>套</t>
+          <t>个</t>
         </is>
       </c>
       <c r="G32" s="25" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="H32" s="25" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I32" s="24">
         <f>E32*G32</f>
@@ -2712,7 +2720,7 @@
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E4</t>
         </is>
       </c>
       <c r="B33" s="22" t="inlineStr">
@@ -2722,12 +2730,12 @@
       </c>
       <c r="C33" s="23" t="inlineStr">
         <is>
-          <t>警示带/围栏线</t>
+          <t>登记本+文具</t>
         </is>
       </c>
       <c r="D33" s="23" t="inlineStr">
         <is>
-          <t>排队动线管理</t>
+          <t>半离线应急登记本 ×3、笔、垫板（RB-04 兜底）</t>
         </is>
       </c>
       <c r="E33" s="24" t="n">
@@ -2739,10 +2747,10 @@
         </is>
       </c>
       <c r="G33" s="25" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H33" s="25" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I33" s="24">
         <f>E33*G33</f>
@@ -2770,7 +2778,7 @@
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="B34" s="22" t="inlineStr">
@@ -2780,12 +2788,12 @@
       </c>
       <c r="C34" s="23" t="inlineStr">
         <is>
-          <t>工具包</t>
+          <t>警示带/围栏线</t>
         </is>
       </c>
       <c r="D34" s="23" t="inlineStr">
         <is>
-          <t>螺丝刀/扎带/绝缘胶带/备用水晶头</t>
+          <t>排队动线管理</t>
         </is>
       </c>
       <c r="E34" s="24" t="n">
@@ -2797,10 +2805,10 @@
         </is>
       </c>
       <c r="G34" s="25" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="H34" s="25" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="I34" s="24">
         <f>E34*G34</f>
@@ -2826,67 +2834,67 @@
       <c r="N34" s="23" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="26" t="inlineStr">
-        <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B35" s="26" t="inlineStr">
-        <is>
-          <t>F 软件与账号</t>
-        </is>
-      </c>
-      <c r="C35" s="27" t="inlineStr">
-        <is>
-          <t>微信小程序账号认证费</t>
-        </is>
-      </c>
-      <c r="D35" s="27" t="inlineStr">
-        <is>
-          <t>学生组织可挂学校主体复用认证则为 0</t>
-        </is>
-      </c>
-      <c r="E35" s="28" t="n">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>E6</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>E 通信与现场物料</t>
+        </is>
+      </c>
+      <c r="C35" s="23" t="inlineStr">
+        <is>
+          <t>工具包</t>
+        </is>
+      </c>
+      <c r="D35" s="23" t="inlineStr">
+        <is>
+          <t>螺丝刀/扎带/绝缘胶带/备用水晶头</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="26" t="inlineStr">
-        <is>
-          <t>项</t>
-        </is>
-      </c>
-      <c r="G35" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="29" t="n">
-        <v>300</v>
-      </c>
-      <c r="I35" s="28">
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>套</t>
+        </is>
+      </c>
+      <c r="G35" s="25" t="n">
+        <v>80</v>
+      </c>
+      <c r="H35" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="I35" s="24">
         <f>E35*G35</f>
         <v/>
       </c>
-      <c r="J35" s="28">
+      <c r="J35" s="24">
         <f>E35*H35</f>
         <v/>
       </c>
-      <c r="K35" s="28">
+      <c r="K35" s="24">
         <f>IF($M35="是",0,I35)</f>
         <v/>
       </c>
-      <c r="L35" s="28">
+      <c r="L35" s="24">
         <f>IF($M35="是",0,J35)</f>
         <v/>
       </c>
-      <c r="M35" s="26" t="inlineStr">
+      <c r="M35" s="22" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="N35" s="27" t="inlineStr"/>
+      <c r="N35" s="23" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="26" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F1</t>
         </is>
       </c>
       <c r="B36" s="26" t="inlineStr">
@@ -2896,12 +2904,12 @@
       </c>
       <c r="C36" s="27" t="inlineStr">
         <is>
-          <t>服务器软件/证书</t>
+          <t>微信小程序账号认证费</t>
         </is>
       </c>
       <c r="D36" s="27" t="inlineStr">
         <is>
-          <t>全自研 Rust + 自签 CA（Debian 开源）</t>
+          <t>学生组织可挂学校主体复用认证则为 0</t>
         </is>
       </c>
       <c r="E36" s="28" t="n">
@@ -2916,7 +2924,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="29" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I36" s="28">
         <f>E36*G36</f>
@@ -2939,16 +2947,12 @@
           <t>否</t>
         </is>
       </c>
-      <c r="N36" s="27" t="inlineStr">
-        <is>
-          <t>0 元</t>
-        </is>
-      </c>
+      <c r="N36" s="27" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="26" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="B37" s="26" t="inlineStr">
@@ -2958,12 +2962,12 @@
       </c>
       <c r="C37" s="27" t="inlineStr">
         <is>
-          <t>域名（方案 B 兜底才需要）</t>
+          <t>云上软件/证书</t>
         </is>
       </c>
       <c r="D37" s="27" t="inlineStr">
         <is>
-          <t>已备案域名 + 证书（见风险 R-01 方案 B）</t>
+          <t>全自研 Rust + 云免费证书（Debian 开源）</t>
         </is>
       </c>
       <c r="E37" s="28" t="n">
@@ -2978,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="H37" s="29" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I37" s="28">
         <f>E37*G37</f>
@@ -3003,7 +3007,7 @@
       </c>
       <c r="N37" s="27" t="inlineStr">
         <is>
-          <t>按需</t>
+          <t>0 元</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3102,7 @@
     <row r="4">
       <c r="A4" s="35" t="inlineStr">
         <is>
-          <t>A 服务器与计算</t>
+          <t>A 云资源与计算</t>
         </is>
       </c>
       <c r="B4" s="36">
@@ -3340,13 +3344,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3357,61 +3361,61 @@
       </c>
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>F1 交易服务器</t>
+          <t>前端聚合机（F1+F2）</t>
         </is>
       </c>
       <c r="C1" s="5" t="inlineStr">
         <is>
-          <t>F2 目录服务器</t>
+          <t>BE 账本机</t>
         </is>
       </c>
       <c r="D1" s="5" t="inlineStr">
         <is>
-          <t>BE 账本服务器</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="40" t="inlineStr">
         <is>
-          <t>主机名 / IP</t>
+          <t>主机名 / 域名</t>
         </is>
       </c>
       <c r="B2" s="40" t="inlineStr">
         <is>
-          <t>f1 / 192.168.10.21</t>
+          <t>edge / edge.&lt;备案域名&gt;（static 回源同机）</t>
         </is>
       </c>
       <c r="C2" s="40" t="inlineStr">
         <is>
-          <t>f2 / 192.168.10.22</t>
+          <t>be / be.&lt;备案域名&gt;</t>
         </is>
       </c>
       <c r="D2" s="40" t="inlineStr">
         <is>
-          <t>be / 192.168.10.23</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="40" t="inlineStr">
         <is>
-          <t>参考规格</t>
+          <t>云规格</t>
         </is>
       </c>
       <c r="B3" s="40" t="inlineStr">
         <is>
-          <t>4C/8G/256G SSD 迷你主机（N100 级）</t>
+          <t>华为云 ECS 16C32G，盘 500G，EIP 带宽峰值 500M（按流量计费）</t>
         </is>
       </c>
       <c r="C3" s="40" t="inlineStr">
         <is>
-          <t>4C/8G/500G SSD（图片存储）</t>
+          <t>华为云 ECS 2C4G，数据盘 40G</t>
         </is>
       </c>
       <c r="D3" s="40" t="inlineStr">
         <is>
-          <t>4C/8G/256G SSD（U 盘备份位）</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3423,7 +3427,7 @@
       </c>
       <c r="B4" s="40" t="inlineStr">
         <is>
-          <t>Debian 12 最小化 + systemd</t>
+          <t>Debian 12 / Ubuntu 22.04 + systemd</t>
         </is>
       </c>
       <c r="C4" s="40" t="inlineStr">
@@ -3433,7 +3437,7 @@
       </c>
       <c r="D4" s="40" t="inlineStr">
         <is>
-          <t>同左</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3445,17 +3449,17 @@
       </c>
       <c r="B5" s="40" t="inlineStr">
         <is>
-          <t>shs-trade（单二进制）</t>
+          <t>Nginx/Caddy 网关(SNI: api/static) + shs-catalog + shs-trade 双进程</t>
         </is>
       </c>
       <c r="C5" s="40" t="inlineStr">
         <is>
-          <t>shs-catalog（单二进制）</t>
+          <t>shs-core（单二进制）</t>
         </is>
       </c>
       <c r="D5" s="40" t="inlineStr">
         <is>
-          <t>shs-core（单二进制）</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3467,17 +3471,17 @@
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
+          <t>443 → 127.0.0.1:8443(catalog)/8444(trade)</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
           <t>443 HTTPS/WSS</t>
         </is>
       </c>
-      <c r="C6" s="40" t="inlineStr">
-        <is>
-          <t>443 HTTPS/WSS</t>
-        </is>
-      </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>443 HTTPS/WSS</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3489,17 +3493,17 @@
       </c>
       <c r="B7" s="40" t="inlineStr">
         <is>
-          <t>registry.db、outbox/*.wal、inventory.snapshot</t>
+          <t>catalog.db、registry.db、outbox/*.wal、inventory.snapshot、/srv/static/</t>
         </is>
       </c>
       <c r="C7" s="40" t="inlineStr">
         <is>
-          <t>catalog.db、/srv/shs/static/</t>
+          <t>core.db（订单/员工/纪念品/审计）</t>
         </is>
       </c>
       <c r="D7" s="40" t="inlineStr">
         <is>
-          <t>core.db（订单/员工/纪念品/审计）</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3515,7 @@
       </c>
       <c r="B8" s="40" t="inlineStr">
         <is>
-          <t>chrony → CPE 出口 NTP 三源</t>
+          <t>云镜像默认 chrony → 云厂商内网 NTP</t>
         </is>
       </c>
       <c r="C8" s="40" t="inlineStr">
@@ -3521,7 +3525,7 @@
       </c>
       <c r="D8" s="40" t="inlineStr">
         <is>
-          <t>同左</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3533,29 +3537,29 @@
       </c>
       <c r="B9" s="40" t="inlineStr">
         <is>
-          <t>WAL 天然持久；活动结束归档双介质</t>
+          <t>云盘快照；活动结束归档双介质</t>
         </is>
       </c>
       <c r="C9" s="40" t="inlineStr">
         <is>
-          <t>目录随包归档</t>
+          <t>每 30min VACUUM INTO + 云快照 + U 盘离线副本</t>
         </is>
       </c>
       <c r="D9" s="40" t="inlineStr">
         <is>
-          <t>每 30min VACUUM INTO + 活动结束全量三备份</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="40" t="inlineStr">
         <is>
-          <t>防火墙</t>
+          <t>安全组</t>
         </is>
       </c>
       <c r="B10" s="40" t="inlineStr">
         <is>
-          <t>443 对 192.168.10.0/24；SSH 仅运维机 .30</t>
+          <t>公网仅 443；SSH 22 仅运维出口 IP + 密钥</t>
         </is>
       </c>
       <c r="C10" s="40" t="inlineStr">
@@ -3565,7 +3569,7 @@
       </c>
       <c r="D10" s="40" t="inlineStr">
         <is>
-          <t>同左</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3577,17 +3581,39 @@
       </c>
       <c r="B11" s="40" t="inlineStr">
         <is>
-          <t>batch_max=50；batch_interval=1s；退避 1/2/4/5/5s</t>
+          <t>batch_max=50；batch_interval=1s；退避 1/2/4/5/5s；图片 webp ≤200KB；匿名限流 30 req/min</t>
         </is>
       </c>
       <c r="C11" s="40" t="inlineStr">
         <is>
-          <t>图片 webp ≤200KB；匿名限流 30 req/min</t>
+          <t>心跳 15s；45s 判离线改派</t>
         </is>
       </c>
       <c r="D11" s="40" t="inlineStr">
         <is>
-          <t>心跳 15s；45s 判离线改派</t>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="inlineStr">
+        <is>
+          <t>故障处置</t>
+        </is>
+      </c>
+      <c r="B12" s="40" t="inlineStr">
+        <is>
+          <t>catalog/trade 进程独立重启；整机故障走云镜像+数据盘 3min 重建</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>重启 ≤30s，WAL/账本无损</t>
+        </is>
+      </c>
+      <c r="D12" s="40" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -3602,7 +3628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3653,17 +3679,17 @@
       </c>
       <c r="B2" s="40" t="inlineStr">
         <is>
-          <t>征借申请发出（学校资产/社团/个人）；全新采购项比价下单</t>
+          <t>域名/备案立即启动（1–3 周）；云 ECS×2 开通初始化；CDN 开通与缓存规则验证</t>
         </is>
       </c>
       <c r="C2" s="41" t="inlineStr">
         <is>
-          <t>成员B</t>
+          <t>成员A/B</t>
         </is>
       </c>
       <c r="D2" s="41" t="inlineStr">
         <is>
-          <t>待办</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="E2" s="41" t="inlineStr"/>
@@ -3677,7 +3703,7 @@
       </c>
       <c r="B3" s="40" t="inlineStr">
         <is>
-          <t>方案 A/B 验证：体验版+调试模式连现场内网真机 spike（R-01）</t>
+          <t>征借申请发出（学校资产/社团/个人）；全新采购项比价下单</t>
         </is>
       </c>
       <c r="C3" s="41" t="inlineStr">
@@ -3690,22 +3716,18 @@
           <t>待办</t>
         </is>
       </c>
-      <c r="E3" s="41" t="inlineStr">
-        <is>
-          <t>全项目最大不确定点，最先消灭</t>
-        </is>
-      </c>
+      <c r="E3" s="41" t="inlineStr"/>
       <c r="F3" s="40" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>W2–W3</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B4" s="40" t="inlineStr">
         <is>
-          <t>到货验收（对照 BOM 逐项打勾）；SIM 办理</t>
+          <t>SIM 核对（已办理√）：确认两卡流量余额 ≥20G、分属两家运营商</t>
         </is>
       </c>
       <c r="C4" s="41" t="inlineStr">
@@ -3715,7 +3737,7 @@
       </c>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>待办</t>
+          <t>已完成</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr"/>
@@ -3724,12 +3746,12 @@
     <row r="5">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>W4–W5</t>
+          <t>W2–W3</t>
         </is>
       </c>
       <c r="B5" s="40" t="inlineStr">
         <is>
-          <t>打印机机型兼容验证（C3 到货即测）；AP 实地试装</t>
+          <t>到货验收（对照 BOM 逐项打勾）</t>
         </is>
       </c>
       <c r="C5" s="41" t="inlineStr">
@@ -3748,17 +3770,17 @@
     <row r="6">
       <c r="A6" s="41" t="inlineStr">
         <is>
-          <t>W6</t>
+          <t>W4–W5</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>全部物料齐套核查；缺项启动替代方案</t>
+          <t>打印机机型兼容验证（C3 到货即测）；AP 实地试装；云上压测（含公网链路）</t>
         </is>
       </c>
       <c r="C6" s="41" t="inlineStr">
         <is>
-          <t>成员A/B</t>
+          <t>成员B</t>
         </is>
       </c>
       <c r="D6" s="41" t="inlineStr">
@@ -3772,12 +3794,12 @@
     <row r="7">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B7" s="40" t="inlineStr">
         <is>
-          <t>彩排全要素使用；耗材按彩排消耗补货</t>
+          <t>全部物料齐套核查；缺项启动替代方案；云资源费用复核</t>
         </is>
       </c>
       <c r="C7" s="41" t="inlineStr">
@@ -3796,17 +3818,17 @@
     <row r="8">
       <c r="A8" s="41" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B8" s="40" t="inlineStr">
         <is>
-          <t>装箱清单（箱号-物料-数量-负责人）随设备运输</t>
+          <t>彩排全要素使用；耗材按彩排消耗补货</t>
         </is>
       </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
-          <t>成员B</t>
+          <t>成员A/B</t>
         </is>
       </c>
       <c r="D8" s="41" t="inlineStr">
@@ -3820,34 +3842,58 @@
     <row r="9">
       <c r="A9" s="41" t="inlineStr">
         <is>
+          <t>W8</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="inlineStr">
+        <is>
+          <t>装箱清单（箱号-物料-数量-负责人）随设备运输</t>
+        </is>
+      </c>
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>成员B</t>
+        </is>
+      </c>
+      <c r="D9" s="41" t="inlineStr">
+        <is>
+          <t>待办</t>
+        </is>
+      </c>
+      <c r="E9" s="41" t="inlineStr"/>
+      <c r="F9" s="40" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="41" t="inlineStr">
+        <is>
           <t>W8+</t>
         </is>
       </c>
-      <c r="B9" s="40" t="inlineStr">
-        <is>
-          <t>设备归还销账；密钥包销毁登记</t>
-        </is>
-      </c>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="B10" s="40" t="inlineStr">
+        <is>
+          <t>ECS 制作最终快照后释放/降配；CDN 停用；设备归还销账；密钥包销毁登记</t>
+        </is>
+      </c>
+      <c r="C10" s="41" t="inlineStr">
         <is>
           <t>成员B</t>
         </is>
       </c>
-      <c r="D9" s="41" t="inlineStr">
+      <c r="D10" s="41" t="inlineStr">
         <is>
           <t>待办</t>
         </is>
       </c>
-      <c r="E9" s="41" t="inlineStr">
+      <c r="E10" s="41" t="inlineStr">
         <is>
           <t>活动结束当日</t>
         </is>
       </c>
-      <c r="F9" s="40" t="n"/>
+      <c r="F10" s="40" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"待办,进行中,已完成,取消"</formula1>
     </dataValidation>
   </dataValidations>
